--- a/results/extensive_linear_90p_p5/estimates/log_extensive_verifiability_fes_normal_p90_p5_both_1000perm_estimates.xlsx
+++ b/results/extensive_linear_90p_p5/estimates/log_extensive_verifiability_fes_normal_p90_p5_both_1000perm_estimates.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -389,14 +389,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ver</t>
+          <t>total_reactions</t>
         </is>
       </c>
       <c r="B2">
-        <v>-0.044308613575612</v>
+        <v>-0.2829922802946696</v>
       </c>
       <c r="C2">
-        <v>0.03283107061114759</v>
+        <v>0.1427798317146223</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -405,7 +405,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>log Verifiable Posts + Shares</t>
+          <t>log(Total reactions)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -417,14 +417,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>non_ver</t>
+          <t>total_comments</t>
         </is>
       </c>
       <c r="B3">
-        <v>-0.08816283643488246</v>
+        <v>-0.1078516023205541</v>
       </c>
       <c r="C3">
-        <v>0.06672800133669905</v>
+        <v>0.0692764749838804</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -433,7 +433,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>log Non Verifiable Posts + Shares</t>
+          <t>log(Total comments)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -445,14 +445,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>total_shares</t>
         </is>
       </c>
       <c r="B4">
-        <v>-0.02319175116657693</v>
+        <v>-0.2712435624330488</v>
       </c>
       <c r="C4">
-        <v>0.01804570295826849</v>
+        <v>0.1467040915099784</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>log True Posts + Shares</t>
+          <t>log(Total shares)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -473,14 +473,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>fake</t>
+          <t>n_posts</t>
         </is>
       </c>
       <c r="B5">
-        <v>-0.03963662206105713</v>
+        <v>-0.1078290035783591</v>
       </c>
       <c r="C5">
-        <v>0.0283720159744345</v>
+        <v>0.07358598511012762</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -489,7 +489,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>log Fake Posts + Shares</t>
+          <t>log(Number of posts + shares)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -501,14 +501,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>n_posts</t>
+          <t>eng</t>
         </is>
       </c>
       <c r="B6">
-        <v>-0.1078290035783591</v>
+        <v>-0.09259870555965094</v>
       </c>
       <c r="C6">
-        <v>0.07358598511012762</v>
+        <v>0.06864271426785791</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -517,7 +517,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>log Number of Posts + Shares</t>
+          <t>log(Number of posts + shares, English)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -529,28 +529,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ver</t>
+          <t>verifiability</t>
         </is>
       </c>
       <c r="B7">
-        <v>-0.0237608050377375</v>
+        <v>-0.044308613575612</v>
       </c>
       <c r="C7">
-        <v>0.02708892862411208</v>
+        <v>0.03283107061114759</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>stage3_4</t>
+          <t>stage1_2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>log Verifiable Posts + Shares</t>
+          <t>log(Verifiable posts + shares)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Weeks 5-8</t>
+          <t>Weeks 1-4</t>
         </is>
       </c>
     </row>
@@ -561,24 +561,24 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.06416612243072736</v>
+        <v>-0.08816283643488246</v>
       </c>
       <c r="C8">
-        <v>0.04749475646378423</v>
+        <v>0.06672800133669905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>stage3_4</t>
+          <t>stage1_2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>log Non Verifiable Posts + Shares</t>
+          <t>log(Non-verifiable posts + shares)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Weeks 5-8</t>
+          <t>Weeks 1-4</t>
         </is>
       </c>
     </row>
@@ -589,24 +589,24 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.0165839481832661</v>
+        <v>-0.02319175116657693</v>
       </c>
       <c r="C9">
-        <v>0.01727704341238711</v>
+        <v>0.01804570295826849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>stage3_4</t>
+          <t>stage1_2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>log True Posts + Shares</t>
+          <t>log(True posts + shares)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Weeks 5-8</t>
+          <t>Weeks 1-4</t>
         </is>
       </c>
     </row>
@@ -617,190 +617,1198 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.01771603989918787</v>
+        <v>-0.03963662206105713</v>
       </c>
       <c r="C10">
-        <v>0.02175309045274668</v>
+        <v>0.0283720159744345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>stage3_4</t>
+          <t>stage1_2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>log Fake Posts + Shares</t>
+          <t>log(Fake posts + shares)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Weeks 5-8</t>
+          <t>Weeks 1-4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>n_posts</t>
+          <t>n_posts_covid</t>
         </is>
       </c>
       <c r="B11">
-        <v>-0.07945069181034994</v>
+        <v>-0.005162637125956833</v>
       </c>
       <c r="C11">
-        <v>0.05748933183302271</v>
+        <v>0.003362707614867721</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>stage3_4</t>
+          <t>stage1_2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>log Number of Posts + Shares</t>
+          <t>log(COVID posts + shares)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Weeks 5-8</t>
+          <t>Weeks 1-4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ver</t>
+          <t>pos_b_covid</t>
         </is>
       </c>
       <c r="B12">
-        <v>-0.02418577393883047</v>
+        <v>-0.002253183869475332</v>
       </c>
       <c r="C12">
-        <v>0.02708164777119759</v>
+        <v>0.001613457571903129</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>stage5_6</t>
+          <t>stage1_2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>log Verifiable Posts + Shares</t>
+          <t>log(Positive COVID posts + shares)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Weeks 9-12</t>
+          <t>Weeks 1-4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>non_ver</t>
+          <t>neutral_b_covid</t>
         </is>
       </c>
       <c r="B13">
-        <v>-0.06539439308201542</v>
+        <v>-0.004063385964998486</v>
       </c>
       <c r="C13">
-        <v>0.04630271574666037</v>
+        <v>0.001496952471414138</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>stage5_6</t>
+          <t>stage1_2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>log Non Verifiable Posts + Shares</t>
+          <t>log(Neutral COVID posts + shares)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Weeks 9-12</t>
+          <t>Weeks 1-4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>neg_b_covid</t>
         </is>
       </c>
       <c r="B14">
-        <v>-0.01809191087024363</v>
+        <v>-0.0005734230462278926</v>
       </c>
       <c r="C14">
-        <v>0.0181476381226825</v>
+        <v>0.001760173355189555</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>stage5_6</t>
+          <t>stage1_2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>log True Posts + Shares</t>
+          <t>log(Negative COVID posts + shares)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Weeks 9-12</t>
+          <t>Weeks 1-4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fake</t>
+          <t>n_posts_vax</t>
         </is>
       </c>
       <c r="B15">
-        <v>-0.02015630091982488</v>
+        <v>0.0003268168174107575</v>
       </c>
       <c r="C15">
-        <v>0.02190130493866894</v>
+        <v>0.0007252667860933309</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>stage5_6</t>
+          <t>stage1_2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>log Fake Posts + Shares</t>
+          <t>log(Vaccine posts + shares)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Weeks 9-12</t>
+          <t>Weeks 1-4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>pos_b_vax</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>0.0002712954617850121</v>
+      </c>
+      <c r="C16">
+        <v>0.0003622228132452747</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>stage1_2</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>log(Positive vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Weeks 1-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>neutral_b_vax</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>-0.0001895439721933908</v>
+      </c>
+      <c r="C17">
+        <v>0.0001918138275006912</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>stage1_2</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>log(Neutral vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Weeks 1-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>neg_b_vax</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>8.947365893880325e-05</v>
+      </c>
+      <c r="C18">
+        <v>0.0004453172488482558</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>stage1_2</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>log(Negative vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Weeks 1-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>total_reactions</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>-0.2325249556353197</v>
+      </c>
+      <c r="C19">
+        <v>0.1205621498183242</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>log(Total reactions)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>total_comments</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>-0.08410545110606144</v>
+      </c>
+      <c r="C20">
+        <v>0.03969342804738669</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>log(Total comments)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>total_shares</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>-0.213070426855726</v>
+      </c>
+      <c r="C21">
+        <v>0.113012004424128</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>log(Total shares)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>n_posts</t>
         </is>
       </c>
-      <c r="B16">
+      <c r="B22">
+        <v>-0.07945069181034994</v>
+      </c>
+      <c r="C22">
+        <v>0.05748933183302271</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>log(Number of posts + shares)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>eng</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>-0.06471932678111819</v>
+      </c>
+      <c r="C23">
+        <v>0.05025817609619789</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>log(Number of posts + shares, English)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>verifiability</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>-0.0237608050377375</v>
+      </c>
+      <c r="C24">
+        <v>0.02708892862411208</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>log(Verifiable posts + shares)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>non_ver</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>-0.06416612243072736</v>
+      </c>
+      <c r="C25">
+        <v>0.04749475646378423</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>log(Non-verifiable posts + shares)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>-0.0165839481832661</v>
+      </c>
+      <c r="C26">
+        <v>0.01727704341238711</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>log(True posts + shares)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>fake</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>-0.01771603989918787</v>
+      </c>
+      <c r="C27">
+        <v>0.02175309045274668</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>log(Fake posts + shares)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>n_posts_covid</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>0.002943092000463454</v>
+      </c>
+      <c r="C28">
+        <v>0.003133902562661798</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>log(COVID posts + shares)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>pos_b_covid</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>-0.0004934108062859889</v>
+      </c>
+      <c r="C29">
+        <v>0.001469881518526566</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>log(Positive COVID posts + shares)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>neutral_b_covid</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>-0.000658487157982252</v>
+      </c>
+      <c r="C30">
+        <v>0.001387356136168721</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>log(Neutral COVID posts + shares)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>neg_b_covid</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>0.003427550328952579</v>
+      </c>
+      <c r="C31">
+        <v>0.002027361875506995</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>log(Negative COVID posts + shares)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>n_posts_vax</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>0.0003316508258177196</v>
+      </c>
+      <c r="C32">
+        <v>0.0007598838238821301</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>log(Vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>pos_b_vax</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>-0.0003289542718475606</v>
+      </c>
+      <c r="C33">
+        <v>0.0004412212200049913</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>log(Positive vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>neutral_b_vax</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>6.438756299675674e-05</v>
+      </c>
+      <c r="C34">
+        <v>0.0002521183906732513</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>log(Neutral vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>neg_b_vax</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>0.0005545049922903751</v>
+      </c>
+      <c r="C35">
+        <v>0.0005328136260268575</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>stage3_4</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>log(Negative vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Weeks 5-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>total_reactions</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>-0.2125709626036189</v>
+      </c>
+      <c r="C36">
+        <v>0.1013669542260924</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>log(Total reactions)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>total_comments</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>-0.08557994656624926</v>
+      </c>
+      <c r="C37">
+        <v>0.03374488444640002</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>log(Total comments)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>total_shares</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>-0.1850177634713466</v>
+      </c>
+      <c r="C38">
+        <v>0.09753786842426508</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>log(Total shares)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>n_posts</t>
+        </is>
+      </c>
+      <c r="B39">
         <v>-0.08043278913979321</v>
       </c>
-      <c r="C16">
+      <c r="C39">
         <v>0.05028765536764152</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>stage5_6</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>log Number of Posts + Shares</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>log(Number of posts + shares)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>eng</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>-0.06307854228623708</v>
+      </c>
+      <c r="C40">
+        <v>0.0444986237439591</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>log(Number of posts + shares, English)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>verifiability</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>-0.02418577393883047</v>
+      </c>
+      <c r="C41">
+        <v>0.02708164777119759</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>log(Verifiable posts + shares)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>non_ver</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>-0.06539439308201542</v>
+      </c>
+      <c r="C42">
+        <v>0.04630271574666037</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>log(Non-verifiable posts + shares)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>-0.01809191087024363</v>
+      </c>
+      <c r="C43">
+        <v>0.0181476381226825</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>log(True posts + shares)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>fake</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>-0.02015630091982488</v>
+      </c>
+      <c r="C44">
+        <v>0.02190130493866894</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>log(Fake posts + shares)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>n_posts_covid</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>0.001657161978392661</v>
+      </c>
+      <c r="C45">
+        <v>0.002928705284586058</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>log(COVID posts + shares)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>pos_b_covid</t>
+        </is>
+      </c>
+      <c r="B46">
+        <v>0.001145483703313283</v>
+      </c>
+      <c r="C46">
+        <v>0.001697187938359224</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>log(Positive COVID posts + shares)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>neutral_b_covid</t>
+        </is>
+      </c>
+      <c r="B47">
+        <v>-0.0006143419546939665</v>
+      </c>
+      <c r="C47">
+        <v>0.001450911178653848</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>log(Neutral COVID posts + shares)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>neg_b_covid</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>0.001266786594597752</v>
+      </c>
+      <c r="C48">
+        <v>0.001392530177457823</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>log(Negative COVID posts + shares)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>n_posts_vax</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>2.890227848220405e-05</v>
+      </c>
+      <c r="C49">
+        <v>0.0006412734420635314</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>log(Vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>pos_b_vax</t>
+        </is>
+      </c>
+      <c r="B50">
+        <v>-0.0002911303422845522</v>
+      </c>
+      <c r="C50">
+        <v>0.0004038393437164204</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>log(Positive vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>neutral_b_vax</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>2.803084152539685e-05</v>
+      </c>
+      <c r="C51">
+        <v>0.0002603276323765695</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>log(Neutral vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Weeks 9-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>neg_b_vax</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>0.0003350821602624622</v>
+      </c>
+      <c r="C52">
+        <v>0.0004284584345661307</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>stage5_6</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>log(Negative vaccine posts + shares)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>Weeks 9-12</t>
         </is>
